--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -467,68 +467,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Старый портал</t>
+          <t>Предупреждение</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8443</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>warning@lab.local</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Unreachable</t>
-        </is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Самоподписанный</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>8443</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>petrov@lab.local</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Unreachable</t>
-        </is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>Старый портал</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>8443</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>petrov@lab.local</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unreachable</t>
-        </is>
+          <t>Expired</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -552,19 +574,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unreachable</t>
-        </is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>364</v>
+      </c>
+      <c r="G5" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ошибка имени</t>
+          <t>Информационный срок</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mismatch.lab.local</t>
+          <t>information.lab.local</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -572,38 +600,164 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sidorov@lab.local</t>
+          <t>info@lab.local</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Unreachable</t>
-        </is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Ошибка имени</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mismatch.lab.local</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sidorov@lab.local</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>364</v>
+      </c>
+      <c r="G7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Wildcard</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>app.wild.lab.local</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8443</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>wildcard@lab.local</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>364</v>
+      </c>
+      <c r="G8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Цепочка</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>chain.lab.local</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>8443</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ca@lab.local</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>364</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Самоподписанный</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>8443</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>364</v>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Недоступный сервис</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>dead.lab.local</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C11" t="n">
         <v>65534</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Unreachable</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сертификаты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сертификаты'!$A$1:$V$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +27,76 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00155724"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00856404"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A84200"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000C5460"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00721C24"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00383D41"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5D0"/>
+        <bgColor rgb="00FFE5D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1ECF1"/>
+        <bgColor rgb="00D1ECF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E3E5"/>
+        <bgColor rgb="00E2E3E5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -48,8 +111,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,148 +485,481 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Сервис</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Хост</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Порт</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Владелец</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Критичность</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SAN</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Issuer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Thumbprint (SHA-1)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Действует с</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Действует до</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Дней осталось</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Дней до окончания</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Цепочка</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Имя совпадает</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Self-signed</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ключ</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Подпись</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Risk Score</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Уровень риска</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Проблемы</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Рекомендации</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Предупреждение</t>
+          <t>HR-портал</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8443</v>
+          <t>chain.lab.local</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>warning@lab.local</t>
+          <t>hr@lab.local</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" t="n">
-        <v>75</v>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>chain.lab.local</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>chain.lab.local</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Radar Lab Rogue CA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4C6AC2BC9834EE5D94FA3B7E66CAC9D1B9CD6CD7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>8443</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>petrov@lab.local</t>
-        </is>
-      </c>
+          <t>warning.lab.local</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>warning.lab.local</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>warning.lab.local</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4FC0C98A3B270C852D71C53FA08BA5F7F1F0C465</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>24.09.2025</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Старый портал</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8443</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>expiring.lab.local</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>petrov@lab.local</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Expired</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>expiring.lab.local</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>expiring.lab.local</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>321906FC68D4B8B0E24EB2B5AC266E1B7438B5B0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>24.09.2025</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Основной веб</t>
+          <t>Портал</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -564,8 +967,10 @@
           <t>valid.lab.local</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>8443</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -574,51 +979,203 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>valid.lab.local</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>valid.lab.local</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>D33CA1D62FF31B12B86332BA33911209F8954572</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>24.09.2025</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12.04.2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>364</v>
-      </c>
-      <c r="G5" t="n">
-        <v>55</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Информационный срок</t>
+          <t>Legacy App</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>information.lab.local</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8443</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>info@lab.local</t>
-        </is>
-      </c>
+          <t>weak.lab.local</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>49</v>
-      </c>
-      <c r="G6" t="n">
-        <v>45</v>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>weak.lab.local</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>weak.lab.local</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>00869CCE4B70161B164CA928E53723F66A34E8A8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>RSA 1024</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>sha1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: EE certificate key too weak (_ssl.c:1010); Слабый ключ: 1024 бит; Устаревший алгоритм подписи: sha1; Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Перевыпустите сертификат с подписью SHA-256 или выше.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ошибка имени</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -626,92 +1183,331 @@
           <t>mismatch.lab.local</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>8443</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sidorov@lab.local</t>
+          <t>api@lab.local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>other.lab.local</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>other.lab.local</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>D3F6D878B24D9A88CFE534600CBE78BD68C738C2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>364</v>
-      </c>
-      <c r="G7" t="n">
-        <v>80</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>Wiki</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>app.wild.lab.local</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8443</v>
+          <t>info.lab.local</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>wildcard@lab.local</t>
+          <t>sidorov@lab.local</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>364</v>
-      </c>
-      <c r="G8" t="n">
-        <v>35</v>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>info.lab.local</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>info.lab.local</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6B049FA011FF40F68B0923289AC53130D647C317</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24.09.2025</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>08.11.2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Цепочка</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8443</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ca@lab.local</t>
-        </is>
-      </c>
+          <t>expired.lab.local</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>364</v>
-      </c>
-      <c r="G9" t="n">
-        <v>35</v>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>expired.lab.local</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>expired.lab.local</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Radar Lab Intermediate CA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FB21A243B3549C444955C7A3401BAB2C531A78A1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>20.08.2025</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Expired</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Срок действия сертификата истёк 5 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Самоподписанный</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -719,26 +1515,111 @@
           <t>selfsigned.lab.local</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>8443</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8443</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ops@lab.local</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>F3DE868B60397C46CC76437FC151BAF1DE0E1264</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>364</v>
-      </c>
-      <c r="G10" t="n">
-        <v>50</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>self_signed</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>RSA 2048</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Недоступный сервис</t>
+          <t>Old Service</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -746,18 +1627,61 @@
           <t>dead.lab.local</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>65534</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8499</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
           <t>Unreachable</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Сервис недоступен: Таймаут соединения</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Проверьте доступность хоста и порта, правила межсетевого экрана и корректность DNS-имени.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:V11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сертификаты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сертификаты'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сертификаты'!$A$1:$Y$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00155724"/>
+      <color rgb="00721C24"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000C5460"/>
     </font>
     <font>
       <b val="1"/>
@@ -40,15 +44,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00A84200"/>
+      <color rgb="00155724"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000C5460"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00721C24"/>
+      <color rgb="00A84200"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,8 +64,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1ECF1"/>
+        <bgColor rgb="00D1ECF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,20 +82,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE5D0"/>
-        <bgColor rgb="00FFE5D0"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
-        <bgColor rgb="00D1ECF1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFE5D0"/>
+        <bgColor rgb="00FFE5D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,19 +497,22 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,65 +563,80 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Thumbprint (SHA-256)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Действует с</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Действует до</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Дней осталось</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Цепочка</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Имя совпадает</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Self-signed</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Ключ</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Подпись</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TLS версия</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Risk Score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Уровень риска</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Проблемы</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Рекомендации</t>
         </is>
@@ -627,12 +645,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HR-портал</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -640,111 +658,118 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>hr@lab.local</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Radar Lab Rogue CA</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4C6AC2BC9834EE5D94FA3B7E66CAC9D1B9CD6CD7</t>
+          <t>3F77EF749ADEA1C0739A1FDA5958B8D18956D3FA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>0525FE3B80727BF336B79F9F87B52FF6A735DA01A2EAE7F62FA3BED59385001E</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>19.09.2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Expired</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>trusted</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Срок действия сертификата истёк 5 дн. назад; Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Wiki</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -752,20 +777,24 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sidorov@lab.local</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -775,84 +804,95 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4FC0C98A3B270C852D71C53FA08BA5F7F1F0C465</t>
+          <t>329758F89A3D2A650E175D0F645B8F8953A38195</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>3DA38BCAAC6303B664F7847B61DDADA6181B9062DE5D6C77045B35B75367CBD9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>19.10.2026</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>08.11.2026</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Information</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>trusted</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 45 дн.</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -860,11 +900,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>petrov@lab.local</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>high</t>
@@ -872,12 +908,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -887,72 +923,83 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>321906FC68D4B8B0E24EB2B5AC266E1B7438B5B0</t>
+          <t>8DEEF85BF0C9D9C37F2D667FD1893E53F57580BE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>1FCAA6F519DD7725818088FD841CFE06CF0CE424643044C8D459420DE542461A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>trusted</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 25 дн.; Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
@@ -999,84 +1046,87 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D33CA1D62FF31B12B86332BA33911209F8954572</t>
+          <t>AA34712445328FD53E97ACE7E7B8C2196C9DADB3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>1A1210CB61C40F6A00A1BDD04716B31CCF62E663A410A7BB975EF0FC149B49A5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>12.04.2027</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>untrusted</t>
-        </is>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>trusted</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legacy App</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1084,103 +1134,122 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ops@lab.local</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>selfsigned.lab.local</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>00869CCE4B70161B164CA928E53723F66A34E8A8</t>
+          <t>1ABAC377C46B5F270227308042BF477B9E3AD20A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>3201275A9D62802569E9FCA20F1B91D5E9F31630265EDAE06CCCE4BAA6A8E995</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>24.09.2027</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>untrusted</t>
-        </is>
-      </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>self_signed</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RSA 1024</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>sha1</t>
+          <t>RSA 2048</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>sha256</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: EE certificate key too weak (_ssl.c:1010); Слабый ключ: 1024 бит; Устаревший алгоритм подписи: sha1; Не назначен владелец сервиса</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Перевыпустите сертификат с подписью SHA-256 или выше.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>HR-портал</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mismatch.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1190,109 +1259,120 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>api@lab.local</t>
+          <t>hr@lab.local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>Radar Lab Rogue CA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D3F6D878B24D9A88CFE534600CBE78BD68C738C2</t>
+          <t>896EDB0325F6CF3B2D1A5F17392407683E763C25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>A167F3DB75A1CE2FFDB7C16A764640AE1243CFF72CC1AB1C1777020D14D580F4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>25.08.2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>24.09.2027</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>365</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wiki</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>mismatch.lab.local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1302,22 +1382,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sidorov@lab.local</t>
+          <t>api@lab.local</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1327,37 +1407,37 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6B049FA011FF40F68B0923289AC53130D647C317</t>
+          <t>6B5D77F9604A8BE0CEB864B8719B8AF1FB06FFA3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>565707BB97AB4F3CD3F8D4714B4903BFEEF6773716359B5C32495DC05593A02F</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>trusted</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1367,44 +1447,55 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1412,7 +1503,11 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>petrov@lab.local</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>high</t>
@@ -1420,12 +1515,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1435,84 +1530,95 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FB21A243B3549C444955C7A3401BAB2C531A78A1</t>
+          <t>CEBBE7317B34F062434ED05718EC12853F066A3E</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>40664BA229989E777C18A5BBA63DB1C00193F5921A1C02AD9620291D17BAFE37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Expired</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>trusted</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Срок действия сертификата истёк 5 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 5 дн.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Legacy App</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1520,99 +1626,106 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ops@lab.local</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>F3DE868B60397C46CC76437FC151BAF1DE0E1264</t>
+          <t>8F9869C708F49DA0500DAAF602D1B14F4C3AFE0A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>F7EF191D3C86AD16EF7E6524AFCE06E8D10F3CBBD888ECE733BA5C9FDBBA025A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>25.08.2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>24.09.2027</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>365</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>self_signed</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>RSA 2048</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>RSA 1024</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность; Слабый ключ: 1024 бит; Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
@@ -1645,43 +1758,50 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Unreachable</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Таймаут соединения</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Сервис недоступен: Таймаут соединения</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Проверьте доступность хоста и порта, правила межсетевого экрана и корректность DNS-имени.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V11"/>
+  <autoFilter ref="A1:Y11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Сертификаты" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сертификаты'!$A$1:$V$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сертификаты'!$A$1:$Y$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,15 +32,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00155724"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00856404"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00A84200"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00155724"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,12 +64,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
@@ -78,6 +72,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFE5D0"/>
         <bgColor rgb="00FFE5D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,19 +497,22 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="43" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="45" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
+    <col width="45" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,65 +563,80 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Thumbprint (SHA-256)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Действует с</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Действует до</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Дней осталось</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Цепочка</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Имя совпадает</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Self-signed</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Ключ</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Подпись</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TLS версия</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Risk Score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Уровень риска</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Проблемы</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Рекомендации</t>
         </is>
@@ -627,12 +645,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HR-портал</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -640,111 +658,118 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>hr@lab.local</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Radar Lab Rogue CA</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4C6AC2BC9834EE5D94FA3B7E66CAC9D1B9CD6CD7</t>
+          <t>8DEEF85BF0C9D9C37F2D667FD1893E53F57580BE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>1FCAA6F519DD7725818088FD841CFE06CF0CE424643044C8D459420DE542461A</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -752,7 +777,11 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>petrov@lab.local</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>high</t>
@@ -760,12 +789,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -775,84 +804,95 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4FC0C98A3B270C852D71C53FA08BA5F7F1F0C465</t>
+          <t>CEBBE7317B34F062434ED05718EC12853F066A3E</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>40664BA229989E777C18A5BBA63DB1C00193F5921A1C02AD9620291D17BAFE37</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>24.09.2025</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>19.10.2026</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Warning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,109 +902,120 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>petrov@lab.local</t>
+          <t>ops@lab.local</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>321906FC68D4B8B0E24EB2B5AC266E1B7438B5B0</t>
+          <t>1ABAC377C46B5F270227308042BF477B9E3AD20A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>3201275A9D62802569E9FCA20F1B91D5E9F31630265EDAE06CCCE4BAA6A8E995</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>self_signed</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Портал</t>
+          <t>HR-портал</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -974,7 +1025,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ivanov@lab.local</t>
+          <t>hr@lab.local</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -984,85 +1035,96 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>Radar Lab Rogue CA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D33CA1D62FF31B12B86332BA33911209F8954572</t>
+          <t>896EDB0325F6CF3B2D1A5F17392407683E763C25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>A167F3DB75A1CE2FFDB7C16A764640AE1243CFF72CC1AB1C1777020D14D580F4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12.04.2027</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
@@ -1071,12 +1133,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legacy App</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>mismatch.lab.local</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1084,58 +1146,66 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>api@lab.local</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>other.lab.local</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>other.lab.local</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>00869CCE4B70161B164CA928E53723F66A34E8A8</t>
+          <t>6B5D77F9604A8BE0CEB864B8719B8AF1FB06FFA3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>565707BB97AB4F3CD3F8D4714B4903BFEEF6773716359B5C32495DC05593A02F</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>24.09.2027</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Нет</t>
@@ -1143,44 +1213,55 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RSA 1024</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>sha1</t>
+          <t>RSA 2048</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>sha256</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: EE certificate key too weak (_ssl.c:1010); Слабый ключ: 1024 бит; Устаревший алгоритм подписи: sha1; Не назначен владелец сервиса</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Перевыпустите сертификат с подписью SHA-256 или выше.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Wiki</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mismatch.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1190,22 +1271,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>api@lab.local</t>
+          <t>sidorov@lab.local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1215,84 +1296,95 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D3F6D878B24D9A88CFE534600CBE78BD68C738C2</t>
+          <t>329758F89A3D2A650E175D0F645B8F8953A38195</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>3DA38BCAAC6303B664F7847B61DDADA6181B9062DE5D6C77045B35B75367CBD9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+          <t>08.11.2026</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
-        </is>
-      </c>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Wiki</t>
+          <t>Legacy App</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1300,11 +1392,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>sidorov@lab.local</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>low</t>
@@ -1312,87 +1400,98 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6B049FA011FF40F68B0923289AC53130D647C317</t>
+          <t>8F9869C708F49DA0500DAAF602D1B14F4C3AFE0A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>F7EF191D3C86AD16EF7E6524AFCE06E8D10F3CBBD888ECE733BA5C9FDBBA025A</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>untrusted</t>
+          <t>24.09.2027</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>self_signed</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>RSA 2048</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>RSA 1024</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность; Слабый ключ: 1024 бит; Не назначен владелец сервиса</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
@@ -1435,70 +1534,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>FB21A243B3549C444955C7A3401BAB2C531A78A1</t>
+          <t>3F77EF749ADEA1C0739A1FDA5958B8D18956D3FA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0525FE3B80727BF336B79F9F87B52FF6A735DA01A2EAE7F62FA3BED59385001E</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>20.08.2025</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>19.09.2026</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>-5</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>Expired</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Срок действия сертификата истёк 5 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
@@ -1507,12 +1617,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>Портал</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1522,7 +1632,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ops@lab.local</t>
+          <t>ivanov@lab.local</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1532,87 +1642,98 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>F3DE868B60397C46CC76437FC151BAF1DE0E1264</t>
+          <t>AA34712445328FD53E97ACE7E7B8C2196C9DADB3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>1A1210CB61C40F6A00A1BDD04716B31CCF62E663A410A7BB975EF0FC149B49A5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
+          <t>12.04.2027</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>self_signed</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>untrusted</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>Да</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>RSA 2048</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>sha256</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>TLSv1.3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
@@ -1645,43 +1766,50 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>Unreachable</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>untrusted</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Таймаут соединения</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>Сервис недоступен: Таймаут соединения</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Проверьте доступность хоста и порта, правила межсетевого экрана и корректность DNS-имени.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V11"/>
+  <autoFilter ref="A1:Y11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -32,10 +32,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00856404"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00A84200"/>
     </font>
     <font>
@@ -52,6 +48,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00856404"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00383D41"/>
     </font>
   </fonts>
@@ -61,12 +61,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -90,6 +84,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
         <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,12 +645,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -658,7 +658,11 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>petrov@lab.local</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>high</t>
@@ -666,12 +670,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -681,12 +685,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8DEEF85BF0C9D9C37F2D667FD1893E53F57580BE</t>
+          <t>321906FC68D4B8B0E24EB2B5AC266E1B7438B5B0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1FCAA6F519DD7725818088FD841CFE06CF0CE424643044C8D459420DE542461A</t>
+          <t>C375BA9D7C7A2936CA148709C79318ED898218482A616EA9F1E9D2DE385BBEAB</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -696,17 +700,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -742,7 +746,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -752,24 +756,24 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
+          <t>Сертификат истекает через 4 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>Портал</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -779,22 +783,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>petrov@lab.local</t>
+          <t>ivanov@lab.local</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -804,12 +808,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CEBBE7317B34F062434ED05718EC12853F066A3E</t>
+          <t>D33CA1D62FF31B12B86332BA33911209F8954572</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40664BA229989E777C18A5BBA63DB1C00193F5921A1C02AD9620291D17BAFE37</t>
+          <t>A06D6D62260AE9DAA78B7491635F355590536649BD93BE86984FE04B62D8D7B9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -819,17 +823,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>12.04.2027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -865,34 +869,34 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>mismatch.lab.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -902,37 +906,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ops@lab.local</t>
+          <t>api@lab.local</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1ABAC377C46B5F270227308042BF477B9E3AD20A</t>
+          <t>D3F6D878B24D9A88CFE534600CBE78BD68C738C2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3201275A9D62802569E9FCA20F1B91D5E9F31630265EDAE06CCCE4BAA6A8E995</t>
+          <t>6C19951486F307762B993D6FC82150175681927633F4E5B7A09FAE37D80FD4E1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -947,27 +951,27 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+          <t>364</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>self_signed</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -988,34 +992,34 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HR-портал</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>hr@lab.local</t>
+          <t>ops@lab.local</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1035,27 +1039,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Radar Lab Rogue CA</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>896EDB0325F6CF3B2D1A5F17392407683E763C25</t>
+          <t>F3DE868B60397C46CC76437FC151BAF1DE0E1264</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>A167F3DB75A1CE2FFDB7C16A764640AE1243CFF72CC1AB1C1777020D14D580F4</t>
+          <t>92F91454E16061B3620DFB4ECE66B3F825DC92CF9B04CA0BE2065646F8422208</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1070,17 +1074,17 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+          <t>364</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>untrusted</t>
+          <t>self_signed</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1090,7 +1094,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1121,24 +1125,24 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Wiki</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mismatch.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1148,22 +1152,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>api@lab.local</t>
+          <t>sidorov@lab.local</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,32 +1177,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6B5D77F9604A8BE0CEB864B8719B8AF1FB06FFA3</t>
+          <t>6B049FA011FF40F68B0923289AC53130D647C317</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>565707BB97AB4F3CD3F8D4714B4903BFEEF6773716359B5C32495DC05593A02F</t>
+          <t>EA058BEDEDD12D44E2F69405A79384EE03EBBCE0E9ED3CA4CCE8084CDC64110A</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>44</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1208,7 +1212,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1234,34 +1238,34 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
+          <t>Сертификат истекает через 44 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wiki</t>
+          <t>Legacy App</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1269,11 +1273,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>sidorov@lab.local</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>low</t>
@@ -1281,47 +1281,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>info.lab.local</t>
-        </is>
-      </c>
+          <t>weak.lab.local</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>329758F89A3D2A650E175D0F645B8F8953A38195</t>
+          <t>00869CCE4B70161B164CA928E53723F66A34E8A8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3DA38BCAAC6303B664F7847B61DDADA6181B9062DE5D6C77045B35B75367CBD9</t>
+          <t>DADE5A63F320E1E745FA25ADACCB90B90631D4DC74A1B71D00EAF8FCF1011600</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>24.09.2027</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>Information</t>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1341,12 +1337,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>RSA 2048</t>
+          <t>RSA 1024</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>sha256</t>
+          <t>sha1</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1357,34 +1353,34 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: EE certificate key too weak (_ssl.c:1010); Слабый ключ: 1024 бит; Устаревший алгоритм подписи: sha1; Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Перевыпустите сертификат с подписью SHA-256 или выше.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Legacy App</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,57 +1391,57 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8F9869C708F49DA0500DAAF602D1B14F4C3AFE0A</t>
+          <t>FB21A243B3549C444955C7A3401BAB2C531A78A1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>F7EF191D3C86AD16EF7E6524AFCE06E8D10F3CBBD888ECE733BA5C9FDBBA025A</t>
+          <t>FA06BE30F4AD77337116E77436646951737D191399F528069382D74EE4655ED8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>19.09.2026</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Expired</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>self_signed</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1455,12 +1451,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>RSA 1024</t>
+          <t>RSA 2048</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1476,34 +1472,34 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность; Слабый ключ: 1024 бит; Не назначен владелец сервиса</t>
+          <t>Срок действия сертификата истёк 6 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HR-портал</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,55 +1507,59 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>hr@lab.local</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>Radar Lab Rogue CA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3F77EF749ADEA1C0739A1FDA5958B8D18956D3FA</t>
+          <t>4C6AC2BC9834EE5D94FA3B7E66CAC9D1B9CD6CD7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0525FE3B80727BF336B79F9F87B52FF6A735DA01A2EAE7F62FA3BED59385001E</t>
+          <t>9B906DDB467F9CA9C8C52E35D2016E839C58B220CD2DD474C350B7581C2131FD</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>24.09.2027</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Expired</t>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1595,34 +1595,34 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Срок действия сертификата истёк 5 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Портал</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,24 +1630,20 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ivanov@lab.local</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1657,12 +1653,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AA34712445328FD53E97ACE7E7B8C2196C9DADB3</t>
+          <t>4FC0C98A3B270C852D71C53FA08BA5F7F1F0C465</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1A1210CB61C40F6A00A1BDD04716B31CCF62E663A410A7BB975EF0FC149B49A5</t>
+          <t>73841609BAC440FE70B28E867A65F58CB05E160EB202F135702439AC3369C35D</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1672,17 +1668,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>12.04.2027</t>
+          <t>19.10.2026</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>Warning</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1718,22 +1714,22 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>95</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
+          <t>Сертификат истекает через 24 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>

--- a/demo/certificates.xlsx
+++ b/demo/certificates.xlsx
@@ -32,7 +32,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00721C24"/>
+      <color rgb="00856404"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A84200"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00155724"/>
     </font>
     <font>
       <b val="1"/>
@@ -40,15 +48,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00856404"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00155724"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00A84200"/>
+      <color rgb="00721C24"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,8 +64,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5D0"/>
+        <bgColor rgb="00FFE5D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,20 +88,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE5D0"/>
-        <bgColor rgb="00FFE5D0"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,12 +645,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VPN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>expired.lab.local</t>
+          <t>warning.lab.local</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -681,37 +681,37 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3F77EF749ADEA1C0739A1FDA5958B8D18956D3FA</t>
+          <t>8DEEF85BF0C9D9C37F2D667FD1893E53F57580BE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0525FE3B80727BF336B79F9F87B52FF6A735DA01A2EAE7F62FA3BED59385001E</t>
+          <t>1FCAA6F519DD7725818088FD841CFE06CF0CE424643044C8D459420DE542461A</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20.08.2025</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>19.10.2026</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -742,7 +742,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>95</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Срок действия сертификата истёк 5 дн. назад; Не назначен владелец сервиса</t>
+          <t>Сертификат истекает через 25 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wiki</t>
+          <t>Почта OWA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -779,22 +779,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sidorov@lab.local</t>
+          <t>petrov@lab.local</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>info.lab.local</t>
+          <t>expiring.lab.local</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>329758F89A3D2A650E175D0F645B8F8953A38195</t>
+          <t>CEBBE7317B34F062434ED05718EC12853F066A3E</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3DA38BCAAC6303B664F7847B61DDADA6181B9062DE5D6C77045B35B75367CBD9</t>
+          <t>40664BA229989E777C18A5BBA63DB1C00193F5921A1C02AD9620291D17BAFE37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -819,22 +819,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08.11.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -865,34 +865,34 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 45 дн.</t>
+          <t>Сертификат истекает через 5 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VPN</t>
+          <t>Jenkins</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -900,60 +900,64 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ops@lab.local</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>warning.lab.local</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>selfsigned.lab.local</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8DEEF85BF0C9D9C37F2D667FD1893E53F57580BE</t>
+          <t>1ABAC377C46B5F270227308042BF477B9E3AD20A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1FCAA6F519DD7725818088FD841CFE06CF0CE424643044C8D459420DE542461A</t>
+          <t>3201275A9D62802569E9FCA20F1B91D5E9F31630265EDAE06CCCE4BAA6A8E995</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>24.09.2027</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>365</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>self_signed</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,7 +967,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -984,34 +988,34 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 25 дн.; Не назначен владелец сервиса</t>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Портал</t>
+          <t>HR-портал</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1021,7 +1025,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ivanov@lab.local</t>
+          <t>hr@lab.local</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1031,52 +1035,52 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>valid.lab.local</t>
+          <t>chain.lab.local</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>Radar Lab Rogue CA</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AA34712445328FD53E97ACE7E7B8C2196C9DADB3</t>
+          <t>896EDB0325F6CF3B2D1A5F17392407683E763C25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1A1210CB61C40F6A00A1BDD04716B31CCF62E663A410A7BB975EF0FC149B49A5</t>
+          <t>A167F3DB75A1CE2FFDB7C16A764640AE1243CFF72CC1AB1C1777020D14D580F4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12.04.2027</t>
+          <t>24.09.2027</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+          <t>365</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1107,26 +1111,34 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jenkins</t>
+          <t>API Gateway</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>mismatch.lab.local</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1136,37 +1148,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ops@lab.local</t>
+          <t>api@lab.local</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>other.lab.local</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>selfsigned.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1ABAC377C46B5F270227308042BF477B9E3AD20A</t>
+          <t>6B5D77F9604A8BE0CEB864B8719B8AF1FB06FFA3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3201275A9D62802569E9FCA20F1B91D5E9F31630265EDAE06CCCE4BAA6A8E995</t>
+          <t>565707BB97AB4F3CD3F8D4714B4903BFEEF6773716359B5C32495DC05593A02F</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1184,24 +1196,24 @@
           <t>365</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>self_signed</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1222,34 +1234,34 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HR-портал</t>
+          <t>Wiki</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1259,57 +1271,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hr@lab.local</t>
+          <t>sidorov@lab.local</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>chain.lab.local</t>
+          <t>info.lab.local</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Radar Lab Rogue CA</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>896EDB0325F6CF3B2D1A5F17392407683E763C25</t>
+          <t>329758F89A3D2A650E175D0F645B8F8953A38195</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A167F3DB75A1CE2FFDB7C16A764640AE1243CFF72CC1AB1C1777020D14D580F4</t>
+          <t>3DA38BCAAC6303B664F7847B61DDADA6181B9062DE5D6C77045B35B75367CBD9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>08.11.2026</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>45</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1355,24 +1367,24 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: self-signed certificate in certificate chain (_ssl.c:1010)</t>
+          <t>Сертификат истекает через 45 дн.; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
+          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>API Gateway</t>
+          <t>Legacy App</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mismatch.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1380,39 +1392,35 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>api@lab.local</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>other.lab.local</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Radar Lab Intermediate CA</t>
+          <t>weak.lab.local</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6B5D77F9604A8BE0CEB864B8719B8AF1FB06FFA3</t>
+          <t>8F9869C708F49DA0500DAAF602D1B14F4C3AFE0A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>565707BB97AB4F3CD3F8D4714B4903BFEEF6773716359B5C32495DC05593A02F</t>
+          <t>F7EF191D3C86AD16EF7E6524AFCE06E8D10F3CBBD888ECE733BA5C9FDBBA025A</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1430,29 +1438,29 @@
           <t>365</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>self_signed</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Нет</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>RSA 2048</t>
+          <t>RSA 1024</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1478,24 +1486,24 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Имя mismatch.lab.local не совпадает с CN/SAN сертификата: other.lab.local</t>
+          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность; Слабый ключ: 1024 бит; Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Перевыпустите сертификат с корректным именем в SAN или исправьте привязку сертификата на сервисе.</t>
+          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Почта OWA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1503,11 +1511,7 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>petrov@lab.local</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>high</t>
@@ -1515,12 +1519,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>expiring.lab.local</t>
+          <t>expired.lab.local</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1530,37 +1534,37 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CEBBE7317B34F062434ED05718EC12853F066A3E</t>
+          <t>3F77EF749ADEA1C0739A1FDA5958B8D18956D3FA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40664BA229989E777C18A5BBA63DB1C00193F5921A1C02AD9620291D17BAFE37</t>
+          <t>0525FE3B80727BF336B79F9F87B52FF6A735DA01A2EAE7F62FA3BED59385001E</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24.09.2025</t>
+          <t>20.08.2025</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>19.09.2026</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Expired</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>trusted</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1591,7 +1595,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1601,24 +1605,24 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Сертификат истекает через 5 дн.</t>
+          <t>Срок действия сертификата истёк 5 дн. назад; Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010); Не назначен владелец сервиса</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Запланируйте перевыпуск и замену сертификата до даты окончания. Назначьте ответственного.</t>
+          <t>Срочно перевыпустите сертификат и установите его на сервис. Проверьте, не нарушена ли работа клиентов.; Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Legacy App</t>
+          <t>Портал</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1626,60 +1630,64 @@
           <t>8443</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ivanov@lab.local</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>valid.lab.local</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>weak.lab.local</t>
+          <t>Radar Lab Intermediate CA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8F9869C708F49DA0500DAAF602D1B14F4C3AFE0A</t>
+          <t>AA34712445328FD53E97ACE7E7B8C2196C9DADB3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>F7EF191D3C86AD16EF7E6524AFCE06E8D10F3CBBD888ECE733BA5C9FDBBA025A</t>
+          <t>1A1210CB61C40F6A00A1BDD04716B31CCF62E663A410A7BB975EF0FC149B49A5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.09.2025</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.09.2027</t>
+          <t>12.04.2027</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>self_signed</t>
+          <t>untrusted</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1689,12 +1697,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Да</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>RSA 1024</t>
+          <t>RSA 2048</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1710,7 +1718,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1720,12 +1728,12 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Сертификат самоподписанный, клиенты не могут проверить его подлинность; Слабый ключ: 1024 бит; Не назначен владелец сервиса</t>
+          <t>Ошибка цепочки доверия: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: certificate signature failure (_ssl.c:1010)</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Замените сертификат на выпущенный корпоративным или публичным центром сертификации.; Перевыпустите сертификат с ключом RSA не менее 2048 бит или ECDSA P-256.; Назначьте ответственного в инвентаре, чтобы уведомления доходили до исполнителя.</t>
+          <t>Установите на сервере полную цепочку (промежуточные сертификаты) или используйте сертификат доверенного центра сертификации.</t>
         </is>
       </c>
     </row>
